--- a/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_04_20_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_04_20_Cau.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -643,7 +643,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hạch toán từng request riêng; phần lịch sử được gửi lại vẫn được tính trong request mới.</t>
+          <t>Tổng số token đầu vào qua ba lượt = 1.000 + 1.800 + 2.600 = 5.400 token. Tổng số token đầu ra qua ba lượt = 3 × 400 = 1.200 token. Tổng số token được hạch toán là 5.400 + 1.200 = 6.600 token.</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -696,7 +696,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giảm phần lặp không liên quan, nhưng không được xóa mù quáng dữ kiện bắt buộc.</t>
+          <t>Các biện pháp giảm chi phí token lặp lại hợp lý: Tóm tắt có kiểm soát lịch sử cũ (a), Chỉ truy xuất đoạn tài liệu liên quan cho từng request (b), và Giới hạn số lượt lịch sử giữ nguyên văn (d). Giữ nguyên toàn bộ nhật ký (c) không giảm chi phí, còn lược bỏ chỉ dẫn bắt buộc (e) làm hỏng chất lượng.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -750,7 +750,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Loại hồ sơ vi phạm giới hạn bắt buộc về ngữ cảnh trước khi so sánh chi phí và chất lượng.</t>
+          <t>Hợp đồng có 90k token đầu vào và 8k token đầu ra (tổng 98k token), vượt giới hạn 32k của Tier S, trong khi Tier L quá đắt vượt ngân sách hạn chế. Do đó Tier M với ngữ cảnh 128k và chi phí vừa phải là lựa chọn phù hợp nhất.</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -862,7 +862,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ mọi yếu tố ngoài danh tính model càng nhất quán càng tốt.</t>
+          <t>Trong thí nghiệm so sánh hai mô hình, mọi yếu tố ngoài danh tính mô hình (e) đều là biến gây nhiễu cần chuẩn hóa: Prompt và ngôn ngữ khác nhau (a), Temperature khác nhau (b), Chỉ chạy 1 lần không đo được phương sai (c), và Ranh giới đo độ trễ khác nhau (d).</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -915,7 +915,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ đủ dữ liệu để người khác tái lập lý do một model được chọn.</t>
+          <t>Để tái lập và kiểm tra lại phép so sánh model, schema kết quả cần ghi nhận: ID mô hình và case_id/prompt (a), Các tham số sinh như temperature, top_p (b), Đầu ra thô và điểm số theo rubric (c), cùng Độ trễ và số token sử dụng (d).</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C, 4-D</t>
+          <t>1-C, 2-B, 3-D, 4-A</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi ai gọi model, qua giao diện nào và ai chịu trách nhiệm về hạ tầng.</t>
+          <t>Cá nhân hỏi đáp thủ công, không cần tích hợp (x1) dùng Giao diện trò chuyện Chat UI (r1); IDE cần gợi ý code theo repository (x2) dùng Trợ lý lập trình coding assistant (r2); Phần backend gọi model theo từng request (x3) dùng API do nhà cung cấp vận hành hosted API (r3); Tổ chức giữ trọng số và suy luận trong hạ tầng riêng (x4) dùng Tự vận hành self-hosted (r4).</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>60</v>
@@ -1021,7 +1021,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn giao diện đáp ứng trường hợp sử dụng hiện tại, không tối ưu cho nhu cầu chưa có.</t>
+          <t>Khi chỉ cần thử nghiệm ý tưởng trong 30 phút bằng vài prompt thủ công mà chưa cần viết code hay tích hợp, Giao diện trò chuyện (Chat UI) là chế độ có chi phí chuẩn bị thấp nhất và nhanh nhất.</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1069,7 +1069,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ kết luận thuộc tính được đo trực tiếp; hãy liệt kê các siêu dữ liệu còn thiếu.</t>
+          <t>Con số công bố `Model X: 300B total parameters` chỉ cho biết quy mô tổng số tham số; nếu là kiến trúc MoE (Mixture of Experts) thì số tham số hoạt động ở mỗi token thấp hơn nhiều, nên chưa đủ dữ kiện để suy ra năng lực tính toán mỗi token hay độ trễ phục vụ.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1117,7 +1117,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp dụng ngưỡng trước, rồi mới tối ưu chỉ số phụ như chi phí.</t>
+          <t>Tiêu chí ưu tiên hàng đầu là độ chính xác thực tế với ngưỡng bắt buộc 92%. Model F chỉ đạt 88% nên bị loại trực tiếp; Model E đạt 94% vượt ngưỡng nên được chọn dù chi phí cao hơn.</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
@@ -1223,7 +1223,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt file cấu hình mẫu với file chứa credential thật, rồi kiểm tra cách xử lý khi biến môi trường không tồn tại.</t>
+          <t>Thực hành an toàn cấu hình: Xóa secret hard-code khỏi source (a), Bỏ track .env và thêm vào .gitignore (b), Giữ .env.example mẫu không có secret thật (c), và Báo lỗi cấu hình rõ ràng trước khi gọi mạng (e). In key ra log (d) là lỗ hổng rò rỉ credential.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1269,7 +1269,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách lỗi cấu hình cục bộ khỏi lỗi do server trả sau lời gọi mạng.</t>
+          <t>Khi `os.getenv('API_KEY')` trả về `None`, cách xử lý đúng là kiểm tra ngay sau khi nạp cấu hình và ném lỗi rõ ràng trước khi thực hiện network call, thay vì gửi đi request lỗi xác thực mơ hồ.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu từng trường với chữ ký hàm được cung cấp; không dùng trí nhớ về SDK khác.</t>
+          <t>Lệnh gọi đúng contract phải truyền đúng các trường: model='m1', messages gồm system message trước rồi đến user message, temperature=0.2 và max_output_tokens=200.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1397,7 +1397,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So cả tên trường lẫn ý nghĩa/giá trị được đặt vào trường đó.</t>
+          <t>Lệnh gọi bị các lỗi: Đặt nhầm content vào role đối nghịch (a), Message order đưa user trước system (b), Tráo giá trị temperature=200 và max_tokens=0.2 (c), trong khi tên phương thức `client.chat.create` vẫn đúng contract (e).</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1443,7 +1443,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đi theo cấu trúc choice → message → content.</t>
+          <t>Cấu trúc phản hồi là dict lồng nhau: để lấy văn bản được sinh từ `{'choices':[{'message':{'content':'Xin chào'}}]}`, biểu thức truy xuất chính xác là `response['choices'][0]['message']['content']`.</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1535,7 +1535,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tên có chữ `output` không đồng nghĩa trường đó chứa văn bản output.</t>
+          <t>Các trường `input_tokens=80`, `output_tokens=20` và `total_tokens=100` đều là các trường số liệu thống kê việc sử dụng token (usage metrics) của request, không chứa nội dung văn bản.</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-A, 2-C, 3-B</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1591,7 +1591,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một `finish_reason` nói về kết thúc bình thường, một về giới hạn output, một về chuyển quyền thực thi hành động.</t>
+          <t>stop (x1) là kết thúc bình thường theo điều kiện dừng (r1); length (x2) là bị cắt do chạm giới hạn token (r2); tool_call (x3) là chuyển sang thực thi/phân phối tool theo contract (r3).</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1637,7 +1637,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy ưu tiên metadata thay vì đoán chỉ từ dấu câu cuối.</t>
+          <t>Khi `finish_reason='length'`, câu trả lời chưa kết thúc tự nhiên mà bị cắt do chạm trần token. Ứng dụng phải đánh dấu bị cắt, không trình bày như câu trả lời hoàn chỉnh, và thực hiện retry có điều chỉnh tăng giới hạn token hoặc yêu cầu viết tiếp có kiểm soát.</t>
         </is>
       </c>
     </row>
